--- a/Field_Section_Compiled_Locked_Format.xlsx
+++ b/Field_Section_Compiled_Locked_Format.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7810" tabRatio="508" activeTab="1"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7810" tabRatio="508"/>
   </bookViews>
   <sheets>
     <sheet name="Corporate Office" sheetId="13" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1811">
   <si>
     <t>Bengaluru Metropolitan Area. Zone Office (South)</t>
   </si>
@@ -3827,9 +3827,6 @@
     <t>Suma nayak</t>
   </si>
   <si>
-    <t>Executive Engineer (IT)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> IT </t>
   </si>
   <si>
@@ -3839,16 +3836,10 @@
     <t>D.D.Jamuna</t>
   </si>
   <si>
-    <t>Executive Engineer (IT SmartGrid)</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT </t>
   </si>
   <si>
     <t>19.04.2021</t>
-  </si>
-  <si>
-    <t>Executive Engineer (IT &amp; Smart Grid)</t>
   </si>
   <si>
     <t>EE(Civil)</t>
@@ -5817,7 +5808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G162"/>
@@ -5856,7 +5847,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -5877,7 +5868,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -5898,7 +5889,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -5909,7 +5900,7 @@
         <v>1086</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>154</v>
@@ -5921,7 +5912,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -5932,7 +5923,7 @@
         <v>1090</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>154</v>
@@ -5944,7 +5935,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -5955,7 +5946,7 @@
         <v>1093</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>154</v>
@@ -5967,7 +5958,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -5978,7 +5969,7 @@
         <v>1097</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>154</v>
@@ -5990,7 +5981,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -6001,7 +5992,7 @@
         <v>1101</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>154</v>
@@ -6013,7 +6004,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -6024,7 +6015,7 @@
         <v>1105</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>154</v>
@@ -6036,7 +6027,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -6047,7 +6038,7 @@
         <v>1109</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>154</v>
@@ -6057,7 +6048,7 @@
       </c>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -6068,7 +6059,7 @@
         <v>1112</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>154</v>
@@ -6080,7 +6071,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -6091,7 +6082,7 @@
         <v>1116</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>154</v>
@@ -6103,7 +6094,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -6114,7 +6105,7 @@
         <v>1119</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>154</v>
@@ -6126,7 +6117,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -6137,7 +6128,7 @@
         <v>1123</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>154</v>
@@ -6149,7 +6140,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -6160,7 +6151,7 @@
         <v>1127</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>154</v>
@@ -6172,7 +6163,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -6183,7 +6174,7 @@
         <v>1130</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>154</v>
@@ -6195,7 +6186,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -6206,7 +6197,7 @@
         <v>1134</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>154</v>
@@ -6218,7 +6209,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -6229,7 +6220,7 @@
         <v>1138</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>154</v>
@@ -6241,7 +6232,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -6252,7 +6243,7 @@
         <v>1141</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>154</v>
@@ -6264,7 +6255,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -6275,7 +6266,7 @@
         <v>1145</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>154</v>
@@ -6287,7 +6278,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -6298,7 +6289,7 @@
         <v>1149</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>154</v>
@@ -6310,7 +6301,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -6321,7 +6312,7 @@
         <v>1152</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>154</v>
@@ -6333,7 +6324,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -6344,7 +6335,7 @@
         <v>1156</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>154</v>
@@ -6356,7 +6347,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -6367,7 +6358,7 @@
         <v>1160</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>154</v>
@@ -6379,7 +6370,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -6390,7 +6381,7 @@
         <v>1163</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>154</v>
@@ -6402,7 +6393,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -6413,7 +6404,7 @@
         <v>1166</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>154</v>
@@ -6425,7 +6416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -6436,7 +6427,7 @@
         <v>1169</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>154</v>
@@ -6448,7 +6439,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -6459,7 +6450,7 @@
         <v>1172</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>154</v>
@@ -6471,7 +6462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -6482,7 +6473,7 @@
         <v>1175</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>154</v>
@@ -6494,7 +6485,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -6505,7 +6496,7 @@
         <v>1177</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>154</v>
@@ -6517,7 +6508,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -6528,7 +6519,7 @@
         <v>1180</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>154</v>
@@ -6540,7 +6531,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -6551,7 +6542,7 @@
         <v>1182</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>154</v>
@@ -6563,7 +6554,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -6574,7 +6565,7 @@
         <v>1186</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>154</v>
@@ -6586,7 +6577,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -6597,7 +6588,7 @@
         <v>1186</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>154</v>
@@ -6609,7 +6600,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -6620,7 +6611,7 @@
         <v>1190</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>154</v>
@@ -6632,7 +6623,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -6643,7 +6634,7 @@
         <v>1194</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>154</v>
@@ -6655,7 +6646,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -6666,7 +6657,7 @@
         <v>1197</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>154</v>
@@ -6678,7 +6669,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -6689,7 +6680,7 @@
         <v>1200</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>154</v>
@@ -6701,7 +6692,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -6712,7 +6703,7 @@
         <v>1204</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>154</v>
@@ -6724,7 +6715,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -6735,7 +6726,7 @@
         <v>1207</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>154</v>
@@ -6747,7 +6738,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -6758,7 +6749,7 @@
         <v>1210</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>154</v>
@@ -6770,7 +6761,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -6781,7 +6772,7 @@
         <v>1212</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>154</v>
@@ -6793,7 +6784,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -6804,7 +6795,7 @@
         <v>1215</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>154</v>
@@ -6816,7 +6807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -6827,7 +6818,7 @@
         <v>1217</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>154</v>
@@ -6839,7 +6830,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -6850,7 +6841,7 @@
         <v>1219</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>154</v>
@@ -6862,7 +6853,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -6873,7 +6864,7 @@
         <v>1219</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>154</v>
@@ -6885,7 +6876,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -6896,7 +6887,7 @@
         <v>1223</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>154</v>
@@ -6908,7 +6899,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -6919,7 +6910,7 @@
         <v>1226</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>154</v>
@@ -6931,7 +6922,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -6942,7 +6933,7 @@
         <v>1227</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>154</v>
@@ -6954,7 +6945,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -6965,7 +6956,7 @@
         <v>1231</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>154</v>
@@ -6977,7 +6968,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -6988,7 +6979,7 @@
         <v>1231</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>154</v>
@@ -7000,7 +6991,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -7011,7 +7002,7 @@
         <v>1231</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>154</v>
@@ -7023,7 +7014,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -7034,7 +7025,7 @@
         <v>1231</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>154</v>
@@ -7046,7 +7037,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -7057,7 +7048,7 @@
         <v>1238</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>154</v>
@@ -7069,7 +7060,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -7080,7 +7071,7 @@
         <v>1241</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>154</v>
@@ -7092,7 +7083,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -7103,7 +7094,7 @@
         <v>1244</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>154</v>
@@ -7115,7 +7106,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -7126,7 +7117,7 @@
         <v>1248</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>154</v>
@@ -7138,7 +7129,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -7149,7 +7140,7 @@
         <v>1250</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>154</v>
@@ -7161,7 +7152,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -7172,7 +7163,7 @@
         <v>1253</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>154</v>
@@ -7184,7 +7175,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -7195,7 +7186,7 @@
         <v>1256</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>154</v>
@@ -7207,7 +7198,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -7218,7 +7209,7 @@
         <v>1259</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>154</v>
@@ -7230,7 +7221,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -7241,7 +7232,7 @@
         <v>1262</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>154</v>
@@ -7260,17 +7251,17 @@
       <c r="B63" s="6" t="s">
         <v>1264</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>1265</v>
+      <c r="C63" s="7" t="s">
+        <v>1226</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>154</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>62</v>
@@ -7281,19 +7272,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>1265</v>
+        <v>1266</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>1226</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>154</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G64" s="8"/>
     </row>
@@ -7302,22 +7293,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>1269</v>
+        <v>1267</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>1226</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>154</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
@@ -7327,19 +7318,19 @@
       <c r="B66" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>1272</v>
+      <c r="C66" s="7" t="s">
+        <v>1226</v>
       </c>
       <c r="D66" s="7"/>
       <c r="E66" s="7" t="s">
         <v>154</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" spans="1:7" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" s="9" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -7347,7 +7338,7 @@
         <v>141</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="D67" s="7"/>
       <c r="E67" s="7" t="s">
@@ -7360,144 +7351,144 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="G68" s="12"/>
     </row>
-    <row r="69" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="G69" s="12" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="G70" s="12"/>
     </row>
-    <row r="71" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="G72" s="12"/>
     </row>
-    <row r="73" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>223</v>
@@ -7507,36 +7498,36 @@
         <v>154</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>169</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -7547,7 +7538,7 @@
         <v>169</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>154</v>
@@ -7557,7 +7548,7 @@
       </c>
       <c r="G76" s="12"/>
     </row>
-    <row r="77" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -7568,19 +7559,19 @@
         <v>169</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -7601,7 +7592,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -7612,7 +7603,7 @@
         <v>169</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>154</v>
@@ -7621,10 +7612,10 @@
         <v>1135</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -7635,7 +7626,7 @@
         <v>169</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>154</v>
@@ -7647,7 +7638,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -7658,19 +7649,19 @@
         <v>169</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -7681,19 +7672,19 @@
         <v>169</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -7704,19 +7695,19 @@
         <v>169</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -7727,17 +7718,17 @@
         <v>169</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="G84" s="12"/>
     </row>
-    <row r="85" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -7748,7 +7739,7 @@
         <v>169</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>154</v>
@@ -7758,7 +7749,7 @@
       </c>
       <c r="G85" s="12"/>
     </row>
-    <row r="86" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -7769,7 +7760,7 @@
         <v>169</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>154</v>
@@ -7781,7 +7772,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -7792,19 +7783,19 @@
         <v>169</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -7815,19 +7806,19 @@
         <v>169</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="E88" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -7838,19 +7829,19 @@
         <v>169</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -7861,19 +7852,19 @@
         <v>169</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -7884,19 +7875,19 @@
         <v>169</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -7907,19 +7898,19 @@
         <v>169</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -7930,19 +7921,19 @@
         <v>169</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -7953,19 +7944,19 @@
         <v>169</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="E94" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -7980,13 +7971,13 @@
         <v>154</v>
       </c>
       <c r="F95" s="11" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G95" s="12" t="s">
         <v>1297</v>
       </c>
-      <c r="G95" s="12" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -7997,7 +7988,7 @@
         <v>169</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="E96" s="11" t="s">
         <v>154</v>
@@ -8009,7 +8000,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -8020,7 +8011,7 @@
         <v>169</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>154</v>
@@ -8032,7 +8023,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -8043,7 +8034,7 @@
         <v>169</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>154</v>
@@ -8055,7 +8046,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -8066,7 +8057,7 @@
         <v>169</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>154</v>
@@ -8076,7 +8067,7 @@
       </c>
       <c r="G99" s="12"/>
     </row>
-    <row r="100" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -8087,19 +8078,19 @@
         <v>169</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -8110,19 +8101,19 @@
         <v>169</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -8133,7 +8124,7 @@
         <v>169</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="E102" s="11" t="s">
         <v>154</v>
@@ -8145,7 +8136,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -8156,19 +8147,19 @@
         <v>169</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="E103" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -8179,7 +8170,7 @@
         <v>169</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="E104" s="11" t="s">
         <v>154</v>
@@ -8191,7 +8182,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -8202,7 +8193,7 @@
         <v>169</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="E105" s="11" t="s">
         <v>154</v>
@@ -8214,7 +8205,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -8225,7 +8216,7 @@
         <v>169</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>154</v>
@@ -8237,7 +8228,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -8248,7 +8239,7 @@
         <v>169</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>154</v>
@@ -8260,7 +8251,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -8271,7 +8262,7 @@
         <v>169</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="E108" s="11" t="s">
         <v>154</v>
@@ -8283,7 +8274,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -8294,7 +8285,7 @@
         <v>169</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>154</v>
@@ -8306,7 +8297,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -8317,7 +8308,7 @@
         <v>169</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="E110" s="11" t="s">
         <v>154</v>
@@ -8329,7 +8320,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -8350,7 +8341,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -8361,7 +8352,7 @@
         <v>169</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>154</v>
@@ -8373,18 +8364,18 @@
         <v>184</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>112</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>169</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>154</v>
@@ -8396,7 +8387,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -8407,7 +8398,7 @@
         <v>169</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="E114" s="11" t="s">
         <v>154</v>
@@ -8419,7 +8410,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -8430,7 +8421,7 @@
         <v>169</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="E115" s="11" t="s">
         <v>154</v>
@@ -8442,7 +8433,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -8453,7 +8444,7 @@
         <v>169</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>154</v>
@@ -8465,7 +8456,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -8476,7 +8467,7 @@
         <v>169</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>154</v>
@@ -8488,7 +8479,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -8499,7 +8490,7 @@
         <v>169</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>154</v>
@@ -8511,7 +8502,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -8522,7 +8513,7 @@
         <v>169</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>154</v>
@@ -8534,18 +8525,18 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>119</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>169</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="E120" s="11" t="s">
         <v>154</v>
@@ -8555,7 +8546,7 @@
       </c>
       <c r="G120" s="12"/>
     </row>
-    <row r="121" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -8566,7 +8557,7 @@
         <v>169</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>154</v>
@@ -8576,7 +8567,7 @@
       </c>
       <c r="G121" s="12"/>
     </row>
-    <row r="122" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -8587,7 +8578,7 @@
         <v>169</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>154</v>
@@ -8599,7 +8590,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -8620,7 +8611,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -8638,10 +8629,10 @@
         <v>1128</v>
       </c>
       <c r="G124" s="12" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -8652,19 +8643,19 @@
         <v>169</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -8675,19 +8666,19 @@
         <v>169</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="E126" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -8698,19 +8689,19 @@
         <v>169</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="G127" s="12" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -8721,19 +8712,19 @@
         <v>169</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="E128" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -8744,19 +8735,19 @@
         <v>169</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="G129" s="12" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -8767,42 +8758,42 @@
         <v>169</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="E130" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="G130" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>130</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>169</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="E131" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -8813,19 +8804,19 @@
         <v>169</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="E132" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -8836,19 +8827,19 @@
         <v>169</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="E133" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="G133" s="12" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -8859,7 +8850,7 @@
         <v>169</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="E134" s="11" t="s">
         <v>154</v>
@@ -8868,10 +8859,10 @@
         <v>1131</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -8882,7 +8873,7 @@
         <v>169</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="E135" s="11" t="s">
         <v>154</v>
@@ -8891,10 +8882,10 @@
         <v>1131</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -8905,19 +8896,19 @@
         <v>169</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="E136" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -8928,19 +8919,19 @@
         <v>169</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="E137" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -8951,19 +8942,19 @@
         <v>169</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="E138" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -8974,19 +8965,19 @@
         <v>169</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="E139" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="G139" s="12" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -8997,19 +8988,19 @@
         <v>169</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="E140" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="G140" s="12" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -9020,19 +9011,19 @@
         <v>169</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="E141" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="G141" s="12" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -9043,19 +9034,19 @@
         <v>169</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="E142" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="G142" s="12" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -9066,19 +9057,19 @@
         <v>169</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="E143" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="G143" s="12" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -9089,19 +9080,19 @@
         <v>169</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="E144" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="G144" s="12" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -9112,19 +9103,19 @@
         <v>169</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="E145" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F145" s="11" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="G145" s="12" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -9135,17 +9126,17 @@
         <v>169</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="E146" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="G146" s="12"/>
     </row>
-    <row r="147" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -9156,19 +9147,19 @@
         <v>169</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="E147" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -9183,13 +9174,13 @@
         <v>154</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -9200,7 +9191,7 @@
         <v>169</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="E149" s="11" t="s">
         <v>154</v>
@@ -9212,7 +9203,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -9223,19 +9214,19 @@
         <v>169</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="E150" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -9246,7 +9237,7 @@
         <v>169</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="E151" s="11" t="s">
         <v>154</v>
@@ -9258,120 +9249,120 @@
         <v>311</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>151</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="E152" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="G152" s="12" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>152</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D153" s="11"/>
       <c r="E153" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>153</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="E154" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>154</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="E155" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>155</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="E156" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="G156" s="12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -9379,45 +9370,45 @@
         <v>245</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="E157" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>157</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="E158" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F158" s="11" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -9425,68 +9416,68 @@
         <v>244</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="E159" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="G159" s="12" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>159</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="E160" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="G160" s="12" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>160</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="E161" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -9494,22 +9485,31 @@
         <v>197</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="E162" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>198</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G162">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Executive Engineer (IT &amp; Smart Grid)"/>
+        <filter val="Executive Engineer (IT SmartGrid)"/>
+        <filter val="Executive Engineer (IT)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -9680,7 +9680,7 @@
         <v>839</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>0</v>
@@ -9700,7 +9700,7 @@
         <v>839</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>3</v>
@@ -9720,7 +9720,7 @@
         <v>839</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>840</v>
@@ -9740,7 +9740,7 @@
         <v>839</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>406</v>
@@ -9760,7 +9760,7 @@
         <v>839</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>463</v>
@@ -9780,7 +9780,7 @@
         <v>839</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>468</v>
@@ -9800,7 +9800,7 @@
         <v>839</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>841</v>
@@ -9820,7 +9820,7 @@
         <v>839</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>469</v>
@@ -9840,7 +9840,7 @@
         <v>839</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>465</v>
@@ -9860,7 +9860,7 @@
         <v>839</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>473</v>
@@ -9880,7 +9880,7 @@
         <v>839</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>477</v>
@@ -9900,7 +9900,7 @@
         <v>839</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>479</v>
@@ -9920,7 +9920,7 @@
         <v>839</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>843</v>
@@ -9940,7 +9940,7 @@
         <v>839</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>484</v>
@@ -9960,7 +9960,7 @@
         <v>844</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>463</v>
@@ -9980,7 +9980,7 @@
         <v>844</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>469</v>
@@ -10000,7 +10000,7 @@
         <v>844</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>465</v>
@@ -10020,7 +10020,7 @@
         <v>844</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>473</v>
@@ -10040,7 +10040,7 @@
         <v>844</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>479</v>
@@ -10060,7 +10060,7 @@
         <v>844</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>843</v>
@@ -10080,7 +10080,7 @@
         <v>844</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>484</v>
@@ -10100,7 +10100,7 @@
         <v>845</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>846</v>
@@ -10120,7 +10120,7 @@
         <v>845</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>40</v>
@@ -10140,7 +10140,7 @@
         <v>845</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>43</v>
@@ -10160,7 +10160,7 @@
         <v>845</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>46</v>
@@ -10180,7 +10180,7 @@
         <v>845</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>847</v>
@@ -10200,7 +10200,7 @@
         <v>845</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>848</v>
@@ -10220,7 +10220,7 @@
         <v>845</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="E35" s="16" t="s">
         <v>52</v>
@@ -10240,7 +10240,7 @@
         <v>845</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>55</v>
@@ -10260,7 +10260,7 @@
         <v>845</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>58</v>
@@ -10280,7 +10280,7 @@
         <v>845</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>849</v>
@@ -10300,7 +10300,7 @@
         <v>845</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="E39" s="16" t="s">
         <v>850</v>
@@ -10320,7 +10320,7 @@
         <v>845</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>1060</v>
@@ -10340,7 +10340,7 @@
         <v>845</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>851</v>
@@ -10360,7 +10360,7 @@
         <v>845</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="E42" s="16" t="s">
         <v>852</v>
@@ -10398,7 +10398,7 @@
         <v>845</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>853</v>
@@ -10418,7 +10418,7 @@
         <v>845</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="E45" s="16" t="s">
         <v>855</v>
@@ -10438,7 +10438,7 @@
         <v>845</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>76</v>
@@ -10458,7 +10458,7 @@
         <v>845</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>856</v>
@@ -10478,7 +10478,7 @@
         <v>845</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>857</v>
@@ -10498,7 +10498,7 @@
         <v>845</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="E49" s="16" t="s">
         <v>858</v>
@@ -10518,7 +10518,7 @@
         <v>845</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>859</v>
@@ -10538,7 +10538,7 @@
         <v>845</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>85</v>
@@ -10558,7 +10558,7 @@
         <v>845</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="E52" s="16" t="s">
         <v>88</v>
@@ -10578,7 +10578,7 @@
         <v>845</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="E53" s="16" t="s">
         <v>90</v>
@@ -10598,7 +10598,7 @@
         <v>845</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="E54" s="16" t="s">
         <v>860</v>
@@ -10618,7 +10618,7 @@
         <v>845</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>95</v>
@@ -10638,7 +10638,7 @@
         <v>845</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="E56" s="16" t="s">
         <v>703</v>
@@ -10658,7 +10658,7 @@
         <v>845</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="E57" s="16" t="s">
         <v>709</v>
@@ -10678,7 +10678,7 @@
         <v>845</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="E58" s="16" t="s">
         <v>102</v>
@@ -10696,7 +10696,7 @@
         <v>845</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="E59" s="16" t="s">
         <v>861</v>
@@ -10716,7 +10716,7 @@
         <v>845</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="E60" s="16" t="s">
         <v>862</v>
@@ -10736,7 +10736,7 @@
         <v>845</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>863</v>
@@ -10756,7 +10756,7 @@
         <v>845</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>109</v>
@@ -10776,7 +10776,7 @@
         <v>845</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="E63" s="16" t="s">
         <v>864</v>
@@ -10796,7 +10796,7 @@
         <v>845</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>113</v>
@@ -10816,7 +10816,7 @@
         <v>845</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="E65" s="16" t="s">
         <v>865</v>
@@ -10836,7 +10836,7 @@
         <v>845</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="E66" s="16" t="s">
         <v>866</v>
@@ -10856,7 +10856,7 @@
         <v>845</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="E67" s="16" t="s">
         <v>117</v>
@@ -10876,7 +10876,7 @@
         <v>845</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="E68" s="16" t="s">
         <v>120</v>
@@ -10896,7 +10896,7 @@
         <v>845</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="E69" s="16" t="s">
         <v>867</v>
@@ -10914,7 +10914,7 @@
         <v>845</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="E70" s="16" t="s">
         <v>124</v>
@@ -10934,7 +10934,7 @@
         <v>845</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="E71" s="16" t="s">
         <v>126</v>
@@ -10954,7 +10954,7 @@
         <v>845</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="E72" s="16" t="s">
         <v>870</v>
@@ -10974,7 +10974,7 @@
         <v>845</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="E73" s="16" t="s">
         <v>130</v>
@@ -10994,7 +10994,7 @@
         <v>845</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="E74" s="16" t="s">
         <v>871</v>
@@ -11014,7 +11014,7 @@
         <v>845</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="E75" s="16" t="s">
         <v>872</v>
@@ -11034,7 +11034,7 @@
         <v>845</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="E76" s="16" t="s">
         <v>873</v>
@@ -11054,7 +11054,7 @@
         <v>845</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="E77" s="16" t="s">
         <v>874</v>
@@ -11164,7 +11164,7 @@
         <v>876</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="E83" s="16" t="s">
         <v>489</v>
@@ -11184,7 +11184,7 @@
         <v>876</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="E84" s="16" t="s">
         <v>878</v>
@@ -11202,7 +11202,7 @@
         <v>876</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="E85" s="16" t="s">
         <v>492</v>
@@ -11222,7 +11222,7 @@
         <v>876</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="E86" s="16" t="s">
         <v>494</v>
@@ -11242,7 +11242,7 @@
         <v>876</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="E87" s="16" t="s">
         <v>497</v>
@@ -11260,7 +11260,7 @@
         <v>876</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="E88" s="16" t="s">
         <v>879</v>
@@ -11280,7 +11280,7 @@
         <v>876</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="E89" s="16" t="s">
         <v>880</v>
@@ -11300,7 +11300,7 @@
         <v>876</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="E90" s="16" t="s">
         <v>881</v>
@@ -11320,7 +11320,7 @@
         <v>876</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="E91" s="16" t="s">
         <v>503</v>
@@ -11340,7 +11340,7 @@
         <v>876</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="E92" s="16" t="s">
         <v>883</v>
@@ -11360,7 +11360,7 @@
         <v>876</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="E93" s="16" t="s">
         <v>884</v>
@@ -11380,7 +11380,7 @@
         <v>876</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="E94" s="16" t="s">
         <v>885</v>
@@ -11400,7 +11400,7 @@
         <v>876</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="E95" s="16" t="s">
         <v>510</v>
@@ -11420,7 +11420,7 @@
         <v>876</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="E96" s="16" t="s">
         <v>886</v>
@@ -11440,7 +11440,7 @@
         <v>876</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="E97" s="16" t="s">
         <v>887</v>
@@ -11460,7 +11460,7 @@
         <v>876</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="E98" s="16" t="s">
         <v>888</v>
@@ -11480,7 +11480,7 @@
         <v>876</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="E99" s="16" t="s">
         <v>889</v>
@@ -11500,7 +11500,7 @@
         <v>876</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="E100" s="16" t="s">
         <v>890</v>
@@ -11520,7 +11520,7 @@
         <v>876</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="E101" s="16" t="s">
         <v>891</v>
@@ -11540,7 +11540,7 @@
         <v>876</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E102" s="16" t="s">
         <v>520</v>
@@ -11578,7 +11578,7 @@
         <v>876</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="E104" s="16" t="s">
         <v>894</v>
@@ -11598,7 +11598,7 @@
         <v>876</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="E105" s="16" t="s">
         <v>895</v>
@@ -11618,7 +11618,7 @@
         <v>876</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="E106" s="16" t="s">
         <v>528</v>
@@ -11638,7 +11638,7 @@
         <v>876</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E107" s="16" t="s">
         <v>531</v>
@@ -11656,7 +11656,7 @@
         <v>876</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="E108" s="16" t="s">
         <v>896</v>
@@ -11674,7 +11674,7 @@
         <v>876</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="E109" s="16" t="s">
         <v>534</v>
@@ -11694,7 +11694,7 @@
         <v>876</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="E110" s="16" t="s">
         <v>898</v>
@@ -11714,7 +11714,7 @@
         <v>876</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="E111" s="16" t="s">
         <v>900</v>
@@ -11734,7 +11734,7 @@
         <v>876</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="E112" s="16" t="s">
         <v>902</v>
@@ -11754,7 +11754,7 @@
         <v>876</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="E113" s="16" t="s">
         <v>903</v>
@@ -11774,7 +11774,7 @@
         <v>876</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="E114" s="16" t="s">
         <v>904</v>
@@ -11794,7 +11794,7 @@
         <v>272</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="E115" s="16" t="s">
         <v>906</v>
@@ -11814,7 +11814,7 @@
         <v>272</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="E116" s="16" t="s">
         <v>907</v>
@@ -11834,7 +11834,7 @@
         <v>272</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="E117" s="16" t="s">
         <v>908</v>
@@ -11852,7 +11852,7 @@
         <v>272</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="E118" s="16" t="s">
         <v>542</v>
@@ -11872,7 +11872,7 @@
         <v>272</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="E119" s="16" t="s">
         <v>544</v>
@@ -11892,7 +11892,7 @@
         <v>272</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="E120" s="16" t="s">
         <v>544</v>
@@ -11930,7 +11930,7 @@
         <v>272</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="E122" s="16" t="s">
         <v>549</v>
@@ -11950,7 +11950,7 @@
         <v>272</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="E123" s="16" t="s">
         <v>909</v>
@@ -11968,7 +11968,7 @@
         <v>272</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="E124" s="16" t="s">
         <v>909</v>
@@ -11986,7 +11986,7 @@
         <v>272</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="E125" s="16" t="s">
         <v>909</v>
@@ -12006,7 +12006,7 @@
         <v>272</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="E126" s="16" t="s">
         <v>553</v>
@@ -12026,7 +12026,7 @@
         <v>272</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>554</v>
@@ -12046,7 +12046,7 @@
         <v>272</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>911</v>
@@ -12064,7 +12064,7 @@
         <v>272</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>912</v>
@@ -12084,7 +12084,7 @@
         <v>272</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>557</v>
@@ -12104,7 +12104,7 @@
         <v>272</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>913</v>
@@ -12124,7 +12124,7 @@
         <v>272</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>561</v>
@@ -12144,7 +12144,7 @@
         <v>272</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>565</v>
@@ -12164,7 +12164,7 @@
         <v>272</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>567</v>
@@ -12184,7 +12184,7 @@
         <v>272</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>914</v>
@@ -12204,7 +12204,7 @@
         <v>272</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>570</v>
@@ -12224,7 +12224,7 @@
         <v>272</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>915</v>
@@ -12244,7 +12244,7 @@
         <v>272</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>916</v>
@@ -12264,7 +12264,7 @@
         <v>272</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>574</v>
@@ -12302,7 +12302,7 @@
         <v>272</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>579</v>
@@ -12322,7 +12322,7 @@
         <v>272</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>581</v>
@@ -12342,7 +12342,7 @@
         <v>272</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>917</v>
@@ -12360,7 +12360,7 @@
         <v>272</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>918</v>
@@ -12378,7 +12378,7 @@
         <v>272</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>919</v>
@@ -12396,7 +12396,7 @@
         <v>272</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>920</v>
@@ -12416,7 +12416,7 @@
         <v>272</v>
       </c>
       <c r="D147" s="16" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>921</v>
@@ -12436,7 +12436,7 @@
         <v>272</v>
       </c>
       <c r="D148" s="16" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>586</v>
@@ -12472,7 +12472,7 @@
         <v>272</v>
       </c>
       <c r="D150" s="16" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="E150" s="16" t="s">
         <v>923</v>
@@ -12492,7 +12492,7 @@
         <v>272</v>
       </c>
       <c r="D151" s="16" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="E151" s="16" t="s">
         <v>924</v>
@@ -12510,7 +12510,7 @@
         <v>272</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="E152" s="16" t="s">
         <v>589</v>
@@ -12530,7 +12530,7 @@
         <v>272</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="E153" s="16" t="s">
         <v>925</v>
@@ -12548,7 +12548,7 @@
         <v>272</v>
       </c>
       <c r="D154" s="16" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="E154" s="16" t="s">
         <v>925</v>
@@ -12568,7 +12568,7 @@
         <v>272</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="E155" s="16" t="s">
         <v>925</v>
@@ -12588,7 +12588,7 @@
         <v>272</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="E156" s="16" t="s">
         <v>593</v>
@@ -12608,7 +12608,7 @@
         <v>272</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="E157" s="16" t="s">
         <v>596</v>
@@ -12628,7 +12628,7 @@
         <v>272</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="E158" s="16" t="s">
         <v>926</v>
@@ -12646,7 +12646,7 @@
         <v>272</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="E159" s="16" t="s">
         <v>927</v>
@@ -12666,7 +12666,7 @@
         <v>272</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="E160" s="16" t="s">
         <v>600</v>
@@ -12686,7 +12686,7 @@
         <v>272</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="E161" s="16" t="s">
         <v>603</v>
@@ -12706,7 +12706,7 @@
         <v>272</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="E162" s="16" t="s">
         <v>928</v>
@@ -12726,7 +12726,7 @@
         <v>272</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="E163" s="16" t="s">
         <v>929</v>
@@ -12746,7 +12746,7 @@
         <v>272</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="E164" s="16" t="s">
         <v>930</v>
@@ -12766,7 +12766,7 @@
         <v>272</v>
       </c>
       <c r="D165" s="16" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="E165" s="16" t="s">
         <v>553</v>
@@ -12786,7 +12786,7 @@
         <v>272</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="E166" s="16" t="s">
         <v>932</v>
@@ -12806,7 +12806,7 @@
         <v>272</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="E167" s="16" t="s">
         <v>933</v>
@@ -12824,7 +12824,7 @@
         <v>272</v>
       </c>
       <c r="D168" s="16" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="E168" s="16" t="s">
         <v>934</v>
@@ -12844,7 +12844,7 @@
         <v>272</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="E169" s="16" t="s">
         <v>935</v>
@@ -12864,7 +12864,7 @@
         <v>272</v>
       </c>
       <c r="D170" s="16" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="E170" s="16" t="s">
         <v>936</v>
@@ -12882,7 +12882,7 @@
         <v>272</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="E171" s="16" t="s">
         <v>937</v>
@@ -12902,7 +12902,7 @@
         <v>272</v>
       </c>
       <c r="D172" s="16" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="E172" s="16" t="s">
         <v>938</v>
@@ -12922,7 +12922,7 @@
         <v>272</v>
       </c>
       <c r="D173" s="16" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="E173" s="16" t="s">
         <v>939</v>
@@ -12940,7 +12940,7 @@
         <v>272</v>
       </c>
       <c r="D174" s="16" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="E174" s="16" t="s">
         <v>333</v>
@@ -12960,7 +12960,7 @@
         <v>272</v>
       </c>
       <c r="D175" s="16" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="E175" s="16" t="s">
         <v>334</v>
@@ -12980,7 +12980,7 @@
         <v>272</v>
       </c>
       <c r="D176" s="16" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="E176" s="16" t="s">
         <v>612</v>
@@ -13000,7 +13000,7 @@
         <v>272</v>
       </c>
       <c r="D177" s="16" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="E177" s="16" t="s">
         <v>613</v>
@@ -13020,7 +13020,7 @@
         <v>272</v>
       </c>
       <c r="D178" s="16" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="E178" s="16" t="s">
         <v>279</v>
@@ -13040,7 +13040,7 @@
         <v>272</v>
       </c>
       <c r="D179" s="16" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="E179" s="16" t="s">
         <v>615</v>
@@ -13060,7 +13060,7 @@
         <v>272</v>
       </c>
       <c r="D180" s="16" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="E180" s="16" t="s">
         <v>616</v>
@@ -13080,7 +13080,7 @@
         <v>272</v>
       </c>
       <c r="D181" s="16" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="E181" s="16" t="s">
         <v>617</v>
@@ -13098,7 +13098,7 @@
         <v>272</v>
       </c>
       <c r="D182" s="16" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="E182" s="16" t="s">
         <v>941</v>
@@ -13154,7 +13154,7 @@
         <v>272</v>
       </c>
       <c r="D185" s="16" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="E185" s="16" t="s">
         <v>468</v>
@@ -13174,7 +13174,7 @@
         <v>272</v>
       </c>
       <c r="D186" s="16" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E186" s="16" t="s">
         <v>942</v>
@@ -13194,7 +13194,7 @@
         <v>272</v>
       </c>
       <c r="D187" s="16" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="E187" s="16" t="s">
         <v>943</v>
@@ -13214,7 +13214,7 @@
         <v>272</v>
       </c>
       <c r="D188" s="16" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="E188" s="16" t="s">
         <v>944</v>
@@ -13234,7 +13234,7 @@
         <v>272</v>
       </c>
       <c r="D189" s="16" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="E189" s="16" t="s">
         <v>620</v>
@@ -13254,7 +13254,7 @@
         <v>272</v>
       </c>
       <c r="D190" s="16" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="E190" s="16" t="s">
         <v>622</v>
@@ -13292,7 +13292,7 @@
         <v>272</v>
       </c>
       <c r="D192" s="16" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="E192" s="16" t="s">
         <v>945</v>
@@ -13312,7 +13312,7 @@
         <v>272</v>
       </c>
       <c r="D193" s="16" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="E193" s="16" t="s">
         <v>945</v>
@@ -13350,7 +13350,7 @@
         <v>272</v>
       </c>
       <c r="D195" s="16" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="E195" s="16" t="s">
         <v>627</v>
@@ -13370,7 +13370,7 @@
         <v>272</v>
       </c>
       <c r="D196" s="16" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="E196" s="16" t="s">
         <v>630</v>
@@ -13388,7 +13388,7 @@
         <v>272</v>
       </c>
       <c r="D197" s="16" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="E197" s="16" t="s">
         <v>946</v>
@@ -13426,7 +13426,7 @@
         <v>272</v>
       </c>
       <c r="D199" s="16" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="E199" s="16" t="s">
         <v>948</v>
@@ -13446,7 +13446,7 @@
         <v>272</v>
       </c>
       <c r="D200" s="16" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="E200" s="16" t="s">
         <v>949</v>
@@ -13466,7 +13466,7 @@
         <v>272</v>
       </c>
       <c r="D201" s="16" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="E201" s="16" t="s">
         <v>950</v>
@@ -13486,7 +13486,7 @@
         <v>272</v>
       </c>
       <c r="D202" s="16" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="E202" s="16" t="s">
         <v>951</v>
@@ -13506,7 +13506,7 @@
         <v>272</v>
       </c>
       <c r="D203" s="16" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="E203" s="16" t="s">
         <v>952</v>
@@ -13524,7 +13524,7 @@
         <v>272</v>
       </c>
       <c r="D204" s="16" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="E204" s="16" t="s">
         <v>953</v>
@@ -13560,7 +13560,7 @@
         <v>272</v>
       </c>
       <c r="D206" s="16" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="E206" s="16" t="s">
         <v>638</v>
@@ -13580,7 +13580,7 @@
         <v>272</v>
       </c>
       <c r="D207" s="16" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="E207" s="16" t="s">
         <v>639</v>
@@ -13600,7 +13600,7 @@
         <v>272</v>
       </c>
       <c r="D208" s="16" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="E208" s="16" t="s">
         <v>955</v>
@@ -13620,7 +13620,7 @@
         <v>272</v>
       </c>
       <c r="D209" s="16" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="E209" s="16" t="s">
         <v>956</v>
@@ -13640,7 +13640,7 @@
         <v>272</v>
       </c>
       <c r="D210" s="16" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="E210" s="16" t="s">
         <v>957</v>
@@ -13660,7 +13660,7 @@
         <v>272</v>
       </c>
       <c r="D211" s="16" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="E211" s="16" t="s">
         <v>958</v>
@@ -13680,7 +13680,7 @@
         <v>272</v>
       </c>
       <c r="D212" s="16" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="E212" s="16" t="s">
         <v>959</v>
@@ -13698,7 +13698,7 @@
         <v>272</v>
       </c>
       <c r="D213" s="16" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="E213" s="16" t="s">
         <v>959</v>
@@ -13718,7 +13718,7 @@
         <v>272</v>
       </c>
       <c r="D214" s="16" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="E214" s="16" t="s">
         <v>959</v>
@@ -13736,7 +13736,7 @@
         <v>272</v>
       </c>
       <c r="D215" s="16" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="E215" s="16" t="s">
         <v>959</v>
@@ -13774,7 +13774,7 @@
         <v>272</v>
       </c>
       <c r="D217" s="16" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="E217" s="16" t="s">
         <v>651</v>
@@ -13792,7 +13792,7 @@
         <v>272</v>
       </c>
       <c r="D218" s="16" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="E218" s="16" t="s">
         <v>960</v>
@@ -13810,7 +13810,7 @@
         <v>272</v>
       </c>
       <c r="D219" s="16" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="E219" s="16" t="s">
         <v>652</v>
@@ -13830,7 +13830,7 @@
         <v>272</v>
       </c>
       <c r="D220" s="16" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="E220" s="16" t="s">
         <v>653</v>
@@ -13850,7 +13850,7 @@
         <v>272</v>
       </c>
       <c r="D221" s="16" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="E221" s="16" t="s">
         <v>961</v>
@@ -13870,7 +13870,7 @@
         <v>272</v>
       </c>
       <c r="D222" s="16" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="E222" s="16" t="s">
         <v>961</v>
@@ -13890,7 +13890,7 @@
         <v>272</v>
       </c>
       <c r="D223" s="16" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="E223" s="16" t="s">
         <v>655</v>
@@ -13910,7 +13910,7 @@
         <v>272</v>
       </c>
       <c r="D224" s="16" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="E224" s="16" t="s">
         <v>962</v>
@@ -13930,7 +13930,7 @@
         <v>272</v>
       </c>
       <c r="D225" s="16" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="E225" s="16" t="s">
         <v>963</v>
@@ -13948,7 +13948,7 @@
         <v>272</v>
       </c>
       <c r="D226" s="16" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="E226" s="16" t="s">
         <v>659</v>
@@ -13968,7 +13968,7 @@
         <v>272</v>
       </c>
       <c r="D227" s="16" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="E227" s="16" t="s">
         <v>660</v>
@@ -13986,7 +13986,7 @@
         <v>272</v>
       </c>
       <c r="D228" s="16" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="E228" s="16" t="s">
         <v>662</v>
@@ -14004,7 +14004,7 @@
         <v>272</v>
       </c>
       <c r="D229" s="16" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="E229" s="16" t="s">
         <v>663</v>
@@ -14022,7 +14022,7 @@
         <v>272</v>
       </c>
       <c r="D230" s="16" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="E230" s="16" t="s">
         <v>664</v>
@@ -14042,7 +14042,7 @@
         <v>272</v>
       </c>
       <c r="D231" s="16" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="E231" s="16" t="s">
         <v>964</v>
@@ -14062,7 +14062,7 @@
         <v>272</v>
       </c>
       <c r="D232" s="16" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="E232" s="16" t="s">
         <v>667</v>
@@ -14082,7 +14082,7 @@
         <v>272</v>
       </c>
       <c r="D233" s="16" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="E233" s="16" t="s">
         <v>669</v>
@@ -14102,7 +14102,7 @@
         <v>272</v>
       </c>
       <c r="D234" s="16" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="E234" s="16" t="s">
         <v>965</v>
@@ -14122,7 +14122,7 @@
         <v>272</v>
       </c>
       <c r="D235" s="16" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="E235" s="16" t="s">
         <v>966</v>
@@ -14142,7 +14142,7 @@
         <v>272</v>
       </c>
       <c r="D236" s="16" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="E236" s="16" t="s">
         <v>967</v>
@@ -14160,7 +14160,7 @@
         <v>272</v>
       </c>
       <c r="D237" s="16" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="E237" s="16" t="s">
         <v>968</v>
@@ -14180,7 +14180,7 @@
         <v>272</v>
       </c>
       <c r="D238" s="16" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="E238" s="16" t="s">
         <v>969</v>
@@ -14200,7 +14200,7 @@
         <v>272</v>
       </c>
       <c r="D239" s="16" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="E239" s="16" t="s">
         <v>970</v>
@@ -14220,7 +14220,7 @@
         <v>272</v>
       </c>
       <c r="D240" s="16" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="E240" s="16" t="s">
         <v>677</v>
@@ -14258,7 +14258,7 @@
         <v>272</v>
       </c>
       <c r="D242" s="16" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="E242" s="16" t="s">
         <v>682</v>
@@ -14294,7 +14294,7 @@
         <v>272</v>
       </c>
       <c r="D244" s="16" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
       <c r="E244" s="16" t="s">
         <v>973</v>
@@ -14350,7 +14350,7 @@
         <v>272</v>
       </c>
       <c r="D247" s="16" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="E247" s="16" t="s">
         <v>357</v>
@@ -14370,7 +14370,7 @@
         <v>272</v>
       </c>
       <c r="D248" s="16" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
       <c r="E248" s="16" t="s">
         <v>686</v>
@@ -14458,7 +14458,7 @@
         <v>272</v>
       </c>
       <c r="D253" s="16" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="E253" s="16" t="s">
         <v>978</v>
@@ -14476,7 +14476,7 @@
         <v>272</v>
       </c>
       <c r="D254" s="16" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="E254" s="16" t="s">
         <v>979</v>
@@ -14496,7 +14496,7 @@
         <v>272</v>
       </c>
       <c r="D255" s="16" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="E255" s="16" t="s">
         <v>980</v>
@@ -14516,7 +14516,7 @@
         <v>272</v>
       </c>
       <c r="D256" s="16" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="E256" s="16" t="s">
         <v>981</v>
@@ -14534,7 +14534,7 @@
         <v>272</v>
       </c>
       <c r="D257" s="16" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="E257" s="16" t="s">
         <v>982</v>
@@ -14590,7 +14590,7 @@
         <v>272</v>
       </c>
       <c r="D260" s="16" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="E260" s="16" t="s">
         <v>985</v>
@@ -14610,7 +14610,7 @@
         <v>272</v>
       </c>
       <c r="D261" s="16" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="E261" s="16" t="s">
         <v>986</v>
@@ -14630,7 +14630,7 @@
         <v>272</v>
       </c>
       <c r="D262" s="16" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="E262" s="16" t="s">
         <v>987</v>
@@ -14668,7 +14668,7 @@
         <v>272</v>
       </c>
       <c r="D264" s="16" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
       <c r="E264" s="16" t="s">
         <v>989</v>
@@ -14688,7 +14688,7 @@
         <v>272</v>
       </c>
       <c r="D265" s="16" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="E265" s="16" t="s">
         <v>990</v>
@@ -14708,7 +14708,7 @@
         <v>272</v>
       </c>
       <c r="D266" s="16" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="E266" s="16" t="s">
         <v>991</v>
@@ -14746,7 +14746,7 @@
         <v>272</v>
       </c>
       <c r="D268" s="16" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
       <c r="E268" s="16" t="s">
         <v>369</v>
@@ -14764,7 +14764,7 @@
         <v>272</v>
       </c>
       <c r="D269" s="16" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="E269" s="16" t="s">
         <v>992</v>
@@ -14782,7 +14782,7 @@
         <v>272</v>
       </c>
       <c r="D270" s="16" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="E270" s="16" t="s">
         <v>373</v>
@@ -14802,7 +14802,7 @@
         <v>272</v>
       </c>
       <c r="D271" s="16" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="E271" s="16" t="s">
         <v>993</v>
@@ -14852,7 +14852,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="15" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="C274" s="16" t="s">
         <v>272</v>
@@ -14892,7 +14892,7 @@
         <v>272</v>
       </c>
       <c r="D276" s="16" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="E276" s="16" t="s">
         <v>377</v>
@@ -14912,7 +14912,7 @@
         <v>272</v>
       </c>
       <c r="D277" s="16" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="E277" s="16" t="s">
         <v>378</v>
@@ -14986,7 +14986,7 @@
         <v>272</v>
       </c>
       <c r="D281" s="16" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="E281" s="16" t="s">
         <v>381</v>
@@ -15006,7 +15006,7 @@
         <v>272</v>
       </c>
       <c r="D282" s="16" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="E282" s="16" t="s">
         <v>717</v>
@@ -15024,7 +15024,7 @@
         <v>272</v>
       </c>
       <c r="D283" s="16" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="E283" s="16" t="s">
         <v>719</v>
@@ -15060,7 +15060,7 @@
         <v>272</v>
       </c>
       <c r="D285" s="16" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="E285" s="16" t="s">
         <v>1000</v>
@@ -15080,10 +15080,10 @@
         <v>272</v>
       </c>
       <c r="D286" s="16" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="E286" s="16" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="F286" s="16" t="s">
         <v>643</v>
@@ -15100,7 +15100,7 @@
         <v>272</v>
       </c>
       <c r="D287" s="16" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="E287" s="16" t="s">
         <v>382</v>
@@ -15118,7 +15118,7 @@
         <v>272</v>
       </c>
       <c r="D288" s="16" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="E288" s="16" t="s">
         <v>383</v>
@@ -15138,7 +15138,7 @@
         <v>272</v>
       </c>
       <c r="D289" s="16" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="E289" s="16" t="s">
         <v>384</v>
@@ -15158,7 +15158,7 @@
         <v>272</v>
       </c>
       <c r="D290" s="16" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="E290" s="16" t="s">
         <v>386</v>
@@ -15172,13 +15172,13 @@
         <v>290</v>
       </c>
       <c r="B291" s="15" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="C291" s="16" t="s">
         <v>272</v>
       </c>
       <c r="D291" s="16" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="E291" s="16" t="s">
         <v>387</v>
@@ -15198,7 +15198,7 @@
         <v>272</v>
       </c>
       <c r="D292" s="16" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="E292" s="16" t="s">
         <v>1001</v>
@@ -15218,7 +15218,7 @@
         <v>272</v>
       </c>
       <c r="D293" s="16" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
       <c r="E293" s="16" t="s">
         <v>726</v>
@@ -15238,7 +15238,7 @@
         <v>272</v>
       </c>
       <c r="D294" s="16" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="E294" s="16" t="s">
         <v>1004</v>
@@ -15258,7 +15258,7 @@
         <v>272</v>
       </c>
       <c r="D295" s="16" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="E295" s="16" t="s">
         <v>391</v>
@@ -15278,7 +15278,7 @@
         <v>272</v>
       </c>
       <c r="D296" s="16" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
       <c r="E296" s="16" t="s">
         <v>729</v>
@@ -15298,7 +15298,7 @@
         <v>272</v>
       </c>
       <c r="D297" s="16" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="E297" s="16" t="s">
         <v>730</v>
@@ -15334,7 +15334,7 @@
         <v>272</v>
       </c>
       <c r="D299" s="16" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="E299" s="16" t="s">
         <v>393</v>
@@ -15354,7 +15354,7 @@
         <v>272</v>
       </c>
       <c r="D300" s="16" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="E300" s="16" t="s">
         <v>395</v>
@@ -15374,7 +15374,7 @@
         <v>272</v>
       </c>
       <c r="D301" s="16" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="E301" s="16" t="s">
         <v>396</v>
@@ -15394,7 +15394,7 @@
         <v>272</v>
       </c>
       <c r="D302" s="16" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="E302" s="16" t="s">
         <v>1009</v>
@@ -15412,7 +15412,7 @@
         <v>272</v>
       </c>
       <c r="D303" s="16" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="E303" s="16" t="s">
         <v>733</v>
@@ -15432,7 +15432,7 @@
         <v>272</v>
       </c>
       <c r="D304" s="16" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="E304" s="16" t="s">
         <v>734</v>
@@ -15488,7 +15488,7 @@
         <v>272</v>
       </c>
       <c r="D307" s="16" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="E307" s="16" t="s">
         <v>738</v>
@@ -15508,7 +15508,7 @@
         <v>272</v>
       </c>
       <c r="D308" s="16" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="E308" s="16" t="s">
         <v>742</v>
@@ -15526,7 +15526,7 @@
         <v>272</v>
       </c>
       <c r="D309" s="16" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="E309" s="16" t="s">
         <v>744</v>
@@ -15546,7 +15546,7 @@
         <v>272</v>
       </c>
       <c r="D310" s="16" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="E310" s="16" t="s">
         <v>745</v>
@@ -15566,7 +15566,7 @@
         <v>272</v>
       </c>
       <c r="D311" s="16" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="E311" s="16" t="s">
         <v>1012</v>
@@ -15586,7 +15586,7 @@
         <v>272</v>
       </c>
       <c r="D312" s="16" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
       <c r="E312" s="16" t="s">
         <v>746</v>
@@ -15606,7 +15606,7 @@
         <v>272</v>
       </c>
       <c r="D313" s="16" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
       <c r="E313" s="16" t="s">
         <v>747</v>
@@ -15626,7 +15626,7 @@
         <v>272</v>
       </c>
       <c r="D314" s="16" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
       <c r="E314" s="16" t="s">
         <v>748</v>
@@ -15646,7 +15646,7 @@
         <v>272</v>
       </c>
       <c r="D315" s="16" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
       <c r="E315" s="16" t="s">
         <v>750</v>
@@ -15682,7 +15682,7 @@
         <v>272</v>
       </c>
       <c r="D317" s="16" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="E317" s="16" t="s">
         <v>406</v>
@@ -15700,7 +15700,7 @@
         <v>272</v>
       </c>
       <c r="D318" s="16" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="E318" s="16" t="s">
         <v>753</v>
@@ -15718,7 +15718,7 @@
         <v>272</v>
       </c>
       <c r="D319" s="16" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="E319" s="16" t="s">
         <v>1015</v>
@@ -15738,7 +15738,7 @@
         <v>272</v>
       </c>
       <c r="D320" s="16" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
       <c r="E320" s="16" t="s">
         <v>1016</v>
@@ -15756,7 +15756,7 @@
         <v>272</v>
       </c>
       <c r="D321" s="16" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
       <c r="E321" s="16" t="s">
         <v>755</v>
@@ -15776,7 +15776,7 @@
         <v>272</v>
       </c>
       <c r="D322" s="16" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
       <c r="E322" s="16" t="s">
         <v>757</v>
@@ -15796,7 +15796,7 @@
         <v>272</v>
       </c>
       <c r="D323" s="16" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="E323" s="16" t="s">
         <v>1017</v>
@@ -15816,7 +15816,7 @@
         <v>272</v>
       </c>
       <c r="D324" s="16" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="E324" s="16" t="s">
         <v>1018</v>
@@ -15836,7 +15836,7 @@
         <v>272</v>
       </c>
       <c r="D325" s="16" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
       <c r="E325" s="16" t="s">
         <v>763</v>
@@ -15856,7 +15856,7 @@
         <v>272</v>
       </c>
       <c r="D326" s="16" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="E326" s="16" t="s">
         <v>765</v>
@@ -15876,7 +15876,7 @@
         <v>272</v>
       </c>
       <c r="D327" s="16" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
       <c r="E327" s="16" t="s">
         <v>1019</v>
@@ -15894,7 +15894,7 @@
         <v>272</v>
       </c>
       <c r="D328" s="16" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="E328" s="16" t="s">
         <v>1020</v>
@@ -15914,7 +15914,7 @@
         <v>272</v>
       </c>
       <c r="D329" s="16" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="E329" s="16" t="s">
         <v>415</v>
@@ -15934,7 +15934,7 @@
         <v>272</v>
       </c>
       <c r="D330" s="16" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
       <c r="E330" s="16" t="s">
         <v>417</v>
@@ -15954,7 +15954,7 @@
         <v>272</v>
       </c>
       <c r="D331" s="16" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="E331" s="16" t="s">
         <v>768</v>
@@ -15974,7 +15974,7 @@
         <v>272</v>
       </c>
       <c r="D332" s="16" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="E332" s="16" t="s">
         <v>1022</v>
@@ -15994,7 +15994,7 @@
         <v>272</v>
       </c>
       <c r="D333" s="16" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="E333" s="16" t="s">
         <v>771</v>
@@ -16014,7 +16014,7 @@
         <v>272</v>
       </c>
       <c r="D334" s="16" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="E334" s="16" t="s">
         <v>419</v>
@@ -16034,7 +16034,7 @@
         <v>272</v>
       </c>
       <c r="D335" s="16" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="E335" s="16" t="s">
         <v>422</v>
@@ -16054,7 +16054,7 @@
         <v>272</v>
       </c>
       <c r="D336" s="16" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="E336" s="16" t="s">
         <v>425</v>
@@ -16074,7 +16074,7 @@
         <v>272</v>
       </c>
       <c r="D337" s="16" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="E337" s="16" t="s">
         <v>773</v>
@@ -16092,7 +16092,7 @@
         <v>272</v>
       </c>
       <c r="D338" s="16" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
       <c r="E338" s="16" t="s">
         <v>1023</v>
@@ -16110,7 +16110,7 @@
         <v>272</v>
       </c>
       <c r="D339" s="16" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="E339" s="16" t="s">
         <v>774</v>
@@ -16130,7 +16130,7 @@
         <v>272</v>
       </c>
       <c r="D340" s="16" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="E340" s="16" t="s">
         <v>429</v>
@@ -16150,7 +16150,7 @@
         <v>272</v>
       </c>
       <c r="D341" s="16" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
       <c r="E341" s="16" t="s">
         <v>1024</v>
@@ -16170,7 +16170,7 @@
         <v>272</v>
       </c>
       <c r="D342" s="16" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="E342" s="16" t="s">
         <v>1025</v>
@@ -16204,7 +16204,7 @@
         <v>272</v>
       </c>
       <c r="D344" s="16" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="E344" s="16" t="s">
         <v>431</v>
@@ -16224,7 +16224,7 @@
         <v>272</v>
       </c>
       <c r="D345" s="16" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="E345" s="16" t="s">
         <v>1026</v>
@@ -16244,7 +16244,7 @@
         <v>272</v>
       </c>
       <c r="D346" s="16" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="E346" s="16" t="s">
         <v>1027</v>
@@ -16264,7 +16264,7 @@
         <v>272</v>
       </c>
       <c r="D347" s="16" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="E347" s="16" t="s">
         <v>1028</v>
@@ -16284,7 +16284,7 @@
         <v>272</v>
       </c>
       <c r="D348" s="16" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="E348" s="16" t="s">
         <v>757</v>
@@ -16304,7 +16304,7 @@
         <v>272</v>
       </c>
       <c r="D349" s="16" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="E349" s="16" t="s">
         <v>1029</v>
@@ -16324,7 +16324,7 @@
         <v>272</v>
       </c>
       <c r="D350" s="16" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="E350" s="16" t="s">
         <v>1029</v>
@@ -16344,7 +16344,7 @@
         <v>272</v>
       </c>
       <c r="D351" s="16" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="E351" s="16" t="s">
         <v>437</v>
@@ -16364,7 +16364,7 @@
         <v>272</v>
       </c>
       <c r="D352" s="16" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="E352" s="16" t="s">
         <v>439</v>
@@ -16384,7 +16384,7 @@
         <v>272</v>
       </c>
       <c r="D353" s="16" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="E353" s="16" t="s">
         <v>784</v>
@@ -16404,7 +16404,7 @@
         <v>272</v>
       </c>
       <c r="D354" s="16" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="E354" s="16" t="s">
         <v>785</v>
@@ -16424,7 +16424,7 @@
         <v>272</v>
       </c>
       <c r="D355" s="16" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="E355" s="16" t="s">
         <v>442</v>
@@ -16444,7 +16444,7 @@
         <v>272</v>
       </c>
       <c r="D356" s="16" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="E356" s="16" t="s">
         <v>444</v>
@@ -16462,7 +16462,7 @@
         <v>272</v>
       </c>
       <c r="D357" s="16" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
       <c r="E357" s="16" t="s">
         <v>788</v>
@@ -16482,7 +16482,7 @@
         <v>272</v>
       </c>
       <c r="D358" s="16" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="E358" s="16" t="s">
         <v>1031</v>
@@ -16502,7 +16502,7 @@
         <v>272</v>
       </c>
       <c r="D359" s="16" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="E359" s="16" t="s">
         <v>790</v>
@@ -16522,7 +16522,7 @@
         <v>272</v>
       </c>
       <c r="D360" s="16" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="E360" s="16" t="s">
         <v>1032</v>
@@ -16542,7 +16542,7 @@
         <v>272</v>
       </c>
       <c r="D361" s="16" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
       <c r="E361" s="16" t="s">
         <v>446</v>
@@ -16560,7 +16560,7 @@
         <v>272</v>
       </c>
       <c r="D362" s="16" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="E362" s="16" t="s">
         <v>1034</v>
@@ -16580,7 +16580,7 @@
         <v>272</v>
       </c>
       <c r="D363" s="16" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
       <c r="E363" s="16" t="s">
         <v>447</v>
@@ -16600,7 +16600,7 @@
         <v>272</v>
       </c>
       <c r="D364" s="16" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
       <c r="E364" s="16" t="s">
         <v>448</v>
@@ -16620,7 +16620,7 @@
         <v>272</v>
       </c>
       <c r="D365" s="16" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="E365" s="16" t="s">
         <v>1045</v>
@@ -16658,7 +16658,7 @@
         <v>272</v>
       </c>
       <c r="D367" s="16" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="E367" s="16" t="s">
         <v>1035</v>
@@ -16678,7 +16678,7 @@
         <v>272</v>
       </c>
       <c r="D368" s="16" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="E368" s="16" t="s">
         <v>1036</v>
@@ -16698,7 +16698,7 @@
         <v>272</v>
       </c>
       <c r="D369" s="16" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
       <c r="E369" s="16" t="s">
         <v>451</v>
@@ -16716,7 +16716,7 @@
         <v>272</v>
       </c>
       <c r="D370" s="16" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="E370" s="16" t="s">
         <v>452</v>
@@ -16736,7 +16736,7 @@
         <v>272</v>
       </c>
       <c r="D371" s="16" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="E371" s="16" t="s">
         <v>454</v>
@@ -16756,7 +16756,7 @@
         <v>272</v>
       </c>
       <c r="D372" s="16" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="E372" s="16" t="s">
         <v>798</v>
@@ -16776,7 +16776,7 @@
         <v>272</v>
       </c>
       <c r="D373" s="16" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
       <c r="E373" s="16" t="s">
         <v>1037</v>
@@ -16796,7 +16796,7 @@
         <v>272</v>
       </c>
       <c r="D374" s="16" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="E374" s="16" t="s">
         <v>1038</v>
@@ -16816,7 +16816,7 @@
         <v>272</v>
       </c>
       <c r="D375" s="16" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="E375" s="16" t="s">
         <v>456</v>
@@ -16836,7 +16836,7 @@
         <v>272</v>
       </c>
       <c r="D376" s="16" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="E376" s="16" t="s">
         <v>457</v>
@@ -16854,7 +16854,7 @@
         <v>272</v>
       </c>
       <c r="D377" s="16" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="E377" s="16" t="s">
         <v>458</v>
@@ -16872,7 +16872,7 @@
         <v>272</v>
       </c>
       <c r="D378" s="16" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="E378" s="16" t="s">
         <v>460</v>
@@ -16892,7 +16892,7 @@
         <v>272</v>
       </c>
       <c r="D379" s="16" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="E379" s="16" t="s">
         <v>461</v>
@@ -16912,7 +16912,7 @@
         <v>272</v>
       </c>
       <c r="D380" s="16" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="E380" s="16" t="s">
         <v>806</v>
@@ -16932,7 +16932,7 @@
         <v>1039</v>
       </c>
       <c r="D381" s="16" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="E381" s="16" t="s">
         <v>1040</v>
@@ -16952,7 +16952,7 @@
         <v>1039</v>
       </c>
       <c r="D382" s="16" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="E382" s="16" t="s">
         <v>1041</v>
@@ -17008,7 +17008,7 @@
         <v>1039</v>
       </c>
       <c r="D385" s="16" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E385" s="16" t="s">
         <v>477</v>
@@ -17046,7 +17046,7 @@
         <v>1039</v>
       </c>
       <c r="D387" s="16" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="E387" s="16" t="s">
         <v>1043</v>
@@ -17066,7 +17066,7 @@
         <v>1039</v>
       </c>
       <c r="D388" s="16" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="E388" s="16" t="s">
         <v>484</v>
